--- a/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week04_21Sep.xlsx
+++ b/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week04_21Sep.xlsx
@@ -1137,7 +1137,7 @@
     <row r="8" ht="33.75" customHeight="1" s="48">
       <c r="A8" s="56" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: International Day of Peace (Mon 21 Sep) — whole-school reflection + calm tutor-time minute.  European Day of Languages Sat 26 Sep — language-taster starter Fri.  EVIDENCE: assembly print + EFL: community → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: International Day of Peace (Mon 21 Sep) — whole-school reflection + calm tutor-time minute.  European Day of Languages Sat 26 Sep — language-taster starter Fri.  EVIDENCE: assembly print + evidence platform: community → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="57" t="n"/>
@@ -1346,7 +1346,7 @@
 Targeted questioning to develop reasoning and operation selection skills.
 Ongoing assessment through observation, discussion and marked work.
 Positive feedback and opportunities for peer support and collaborative learning.
-LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily evidence platform].</t>
         </is>
       </c>
       <c r="J11" s="67" t="inlineStr">
@@ -1451,7 +1451,7 @@
       <c r="I13" s="67" t="inlineStr">
         <is>
           <t>TA joins the panel to model reasoning aloud; teacher gives the 'what the law says' reveal with live feedback each round; photos are the evidence.
-LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to EFL, same day [E: PfA/citizenship/social enterprise — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to evidence platform, same day [E: PfA/citizenship/social enterprise — daily evidence platform].</t>
         </is>
       </c>
       <c r="J13" s="67" t="inlineStr">
